--- a/artfynd/A 5834-2026 artfynd.xlsx
+++ b/artfynd/A 5834-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,6 +905,426 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131539095</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57076</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bjälkåsemossen, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>325773</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6447594</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131539178</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57076</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bjälkåsemossen, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>325900</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6447584</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131538901</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57076</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bjälkåsemossen, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>325632</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6447597</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131539117</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57076</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bjälkåsemossen, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>325829</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6447578</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5834-2026 artfynd.xlsx
+++ b/artfynd/A 5834-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131522161</v>
       </c>
       <c r="B2" t="n">
-        <v>80915</v>
+        <v>80918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131522098</v>
       </c>
       <c r="B3" t="n">
-        <v>80915</v>
+        <v>80918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>131539095</v>
       </c>
       <c r="B4" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>131539178</v>
       </c>
       <c r="B5" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>131538901</v>
       </c>
       <c r="B6" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>131539117</v>
       </c>
       <c r="B7" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5834-2026 artfynd.xlsx
+++ b/artfynd/A 5834-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131522161</v>
       </c>
       <c r="B2" t="n">
-        <v>80918</v>
+        <v>80919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131522098</v>
       </c>
       <c r="B3" t="n">
-        <v>80918</v>
+        <v>80919</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>131539095</v>
       </c>
       <c r="B4" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>131539178</v>
       </c>
       <c r="B5" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>131538901</v>
       </c>
       <c r="B6" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>131539117</v>
       </c>
       <c r="B7" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5834-2026 artfynd.xlsx
+++ b/artfynd/A 5834-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131522161</v>
+        <v>131538901</v>
       </c>
       <c r="B2" t="n">
-        <v>80941</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>230185</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325780</v>
+        <v>325632</v>
       </c>
       <c r="R2" t="n">
-        <v>6447738</v>
+        <v>6447597</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,40 +756,34 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På barken av äldre ek, nära mosse (fanns på 2 ekar) i barrdominerad blandskog.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131522098</v>
+        <v>131539095</v>
       </c>
       <c r="B3" t="n">
-        <v>80941</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,26 +791,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230185</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -819,13 +823,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325792</v>
+        <v>325773</v>
       </c>
       <c r="R3" t="n">
-        <v>6447728</v>
+        <v>6447594</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,54 +867,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Lövträd</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Blandskkog, barrdominerat med inslag av ek nära mosse</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>ekar</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Quercus</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Quercus</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131539095</v>
+        <v>131539117</v>
       </c>
       <c r="B4" t="n">
-        <v>57102</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -950,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325773</v>
+        <v>325829</v>
       </c>
       <c r="R4" t="n">
-        <v>6447594</v>
+        <v>6447578</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1015,7 +993,7 @@
         <v>131539178</v>
       </c>
       <c r="B5" t="n">
-        <v>57102</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131538901</v>
+        <v>131539222</v>
       </c>
       <c r="B6" t="n">
-        <v>57102</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325632</v>
+        <v>325871</v>
       </c>
       <c r="R6" t="n">
-        <v>6447597</v>
+        <v>6447487</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,56 +1200,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131539117</v>
+        <v>124326774</v>
       </c>
       <c r="B7" t="n">
-        <v>57102</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjälkåsemossen, Boh</t>
+          <t>Lilla Edet, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325829</v>
+        <v>325857</v>
       </c>
       <c r="R7" t="n">
-        <v>6447578</v>
+        <v>6447353</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,12 +1269,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>En kvadratmeters täckning. Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,15 +1294,366 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131532034</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bjälkåsemossen, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>325836</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6447345</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>15-20 bladpar i olika mindre storlekar.  Sveaskogs egen biolog (?) har i april 2025 rapporterat in 1 ex på samma plats.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Liv Vikingson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Liv Vikingson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131522098</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bjälkåsemossen, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>325792</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6447728</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Lövträd</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Blandskkog, barrdominerat med inslag av ek nära mosse</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ekar</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Quercus</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Quercus</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131522161</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bjälkåsemossen, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>325780</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6447738</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På barken av äldre ek, nära mosse (fanns på 2 ekar) i barrdominerad blandskog.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5834-2026 artfynd.xlsx
+++ b/artfynd/A 5834-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131538901</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131539095</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131539117</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131539178</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131539222</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124326774</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,6 +1457,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131532034</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131522098</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1654,8 +1699,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131522161</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>